--- a/Employee_Reports_wi52/Peter Nganga Kamau Q0593.xlsx
+++ b/Employee_Reports_wi52/Peter Nganga Kamau Q0593.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-53</v>
+        <v>-61</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1525,20 +1525,20 @@
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>315</v>
+        <v>726</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
